--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>136336934</v>
       </c>
       <c r="B10" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136336942</v>
       </c>
       <c r="B52" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136336929</v>
       </c>
       <c r="B193" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136336930</v>
       </c>
       <c r="B194" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136336936</v>
       </c>
       <c r="B195" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136336937</v>
       </c>
       <c r="B196" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136336938</v>
       </c>
       <c r="B197" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>136336943</v>
       </c>
       <c r="B198" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>136336947</v>
       </c>
       <c r="B199" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136336949</v>
       </c>
       <c r="B200" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136336950</v>
       </c>
       <c r="B201" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>136336951</v>
       </c>
       <c r="B202" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>136336955</v>
       </c>
       <c r="B203" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>136336958</v>
       </c>
       <c r="B204" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>136336961</v>
       </c>
       <c r="B205" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>136336963</v>
       </c>
       <c r="B206" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>136336964</v>
       </c>
       <c r="B207" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>136336968</v>
       </c>
       <c r="B208" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>136336940</v>
       </c>
       <c r="B218" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>136336952</v>
       </c>
       <c r="B219" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>136336959</v>
       </c>
       <c r="B220" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>136336932</v>
       </c>
       <c r="B221" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>136336956</v>
       </c>
       <c r="B222" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>136336944</v>
       </c>
       <c r="B248" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>136336945</v>
       </c>
       <c r="B249" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>136336935</v>
       </c>
       <c r="B257" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>136336931</v>
       </c>
       <c r="B287" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136336939</v>
       </c>
       <c r="B288" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>136336948</v>
       </c>
       <c r="B289" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>136336954</v>
       </c>
       <c r="B290" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>136336960</v>
       </c>
       <c r="B291" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>136336965</v>
       </c>
       <c r="B292" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>136336934</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136336942</v>
       </c>
       <c r="B52" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136336929</v>
       </c>
       <c r="B193" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136336930</v>
       </c>
       <c r="B194" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136336936</v>
       </c>
       <c r="B195" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136336937</v>
       </c>
       <c r="B196" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136336938</v>
       </c>
       <c r="B197" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>136336943</v>
       </c>
       <c r="B198" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>136336947</v>
       </c>
       <c r="B199" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136336949</v>
       </c>
       <c r="B200" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136336950</v>
       </c>
       <c r="B201" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>136336951</v>
       </c>
       <c r="B202" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>136336955</v>
       </c>
       <c r="B203" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>136336958</v>
       </c>
       <c r="B204" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>136336961</v>
       </c>
       <c r="B205" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>136336963</v>
       </c>
       <c r="B206" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>136336964</v>
       </c>
       <c r="B207" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>136336968</v>
       </c>
       <c r="B208" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>136336940</v>
       </c>
       <c r="B218" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>136336952</v>
       </c>
       <c r="B219" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>136336959</v>
       </c>
       <c r="B220" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>136336932</v>
       </c>
       <c r="B221" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>136336956</v>
       </c>
       <c r="B222" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>136336934</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136336942</v>
       </c>
       <c r="B52" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136336929</v>
       </c>
       <c r="B193" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136336930</v>
       </c>
       <c r="B194" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136336936</v>
       </c>
       <c r="B195" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136336937</v>
       </c>
       <c r="B196" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136336938</v>
       </c>
       <c r="B197" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>136336943</v>
       </c>
       <c r="B198" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>136336947</v>
       </c>
       <c r="B199" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136336949</v>
       </c>
       <c r="B200" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136336950</v>
       </c>
       <c r="B201" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>136336951</v>
       </c>
       <c r="B202" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>136336955</v>
       </c>
       <c r="B203" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>136336958</v>
       </c>
       <c r="B204" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>136336961</v>
       </c>
       <c r="B205" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>136336963</v>
       </c>
       <c r="B206" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>136336964</v>
       </c>
       <c r="B207" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>136336968</v>
       </c>
       <c r="B208" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>136336940</v>
       </c>
       <c r="B218" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>136336952</v>
       </c>
       <c r="B219" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>136336959</v>
       </c>
       <c r="B220" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>136336932</v>
       </c>
       <c r="B221" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>136336956</v>
       </c>
       <c r="B222" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>136336931</v>
       </c>
       <c r="B287" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136336939</v>
       </c>
       <c r="B288" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>136336948</v>
       </c>
       <c r="B289" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>136336954</v>
       </c>
       <c r="B290" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>136336960</v>
       </c>
       <c r="B291" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>136336965</v>
       </c>
       <c r="B292" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
